--- a/Planificacion/Costo_Estimado.xlsx
+++ b/Planificacion/Costo_Estimado.xlsx
@@ -1,19 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/93290c276c767585/Desktop/motogo/Planificacion/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_C4A46FE1E199D6D94E9442D8819BC8AF07816425" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C75073E5-D5D3-4D08-B522-2B8C2C69A123}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="EMPLEADOS " sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="SERVICIOS" sheetId="3" r:id="rId7"/>
+    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
+    <sheet name="EMPLEADOS " sheetId="2" r:id="rId2"/>
+    <sheet name="SERVICIOS" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="76">
   <si>
     <t>Cuadro Comparativo de Cotizaciones para MOTOGO</t>
   </si>
@@ -255,103 +264,122 @@
   </si>
   <si>
     <t>$ 17.500,00</t>
+  </si>
+  <si>
+    <t>la mas perra</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="19">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
-    <font/>
-    <font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <i/>
-      <sz val="8.0"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="&quot;Trebuchet MS&quot;"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;Trebuchet MS&quot;"/>
     </font>
     <font>
       <i/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;Trebuchet MS&quot;"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
-    </font>
-    <font>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF231F20"/>
       <name val="&quot;Trebuchet MS&quot;"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="&quot;Trebuchet MS&quot;"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;Trebuchet MS&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="&quot;Trebuchet MS&quot;"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
@@ -361,7 +389,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -425,41 +453,39 @@
     </fill>
   </fills>
   <borders count="11">
-    <border/>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -469,46 +495,64 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -517,245 +561,177 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="60">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="4" fillId="0" fontId="14" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="14" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="9" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="6" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="17" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="15" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="10" fillId="7" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="15" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="7" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="8" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="9" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="10" fontId="15" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="11" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="4" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="10" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -763,7 +739,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -953,799 +929,806 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A4:L17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="26.5"/>
-    <col customWidth="1" min="3" max="3" width="58.75"/>
-    <col customWidth="1" min="4" max="4" width="24.5"/>
-    <col customWidth="1" min="5" max="5" width="14.38"/>
-    <col customWidth="1" min="6" max="6" width="92.88"/>
-    <col customWidth="1" min="8" max="8" width="18.5"/>
-    <col customWidth="1" min="11" max="11" width="20.5"/>
+    <col min="2" max="2" width="26.44140625" customWidth="1"/>
+    <col min="3" max="3" width="58.77734375" customWidth="1"/>
+    <col min="4" max="4" width="24.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="6" max="6" width="92.88671875" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" customWidth="1"/>
+    <col min="11" max="11" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A4" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="10"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="s">
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="s">
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="s">
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="s">
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="21"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="s">
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="18"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="I12" s="25" t="s">
+      <c r="I12" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="K12" s="25" t="s">
+      <c r="K12" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="L12" s="25" t="s">
+      <c r="L12" s="21" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="s">
+    <row r="13" spans="1:12">
+      <c r="A13" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="26">
-        <v>1750905.0</v>
-      </c>
-      <c r="D13" s="27">
-        <v>249095.0</v>
-      </c>
-      <c r="E13" s="28">
-        <v>148827.0</v>
-      </c>
-      <c r="F13" s="29">
-        <v>210108.0</v>
-      </c>
-      <c r="G13" s="30">
-        <v>9014.0</v>
-      </c>
-      <c r="H13" s="30">
-        <v>70036.0</v>
-      </c>
-      <c r="I13" s="30">
-        <v>145873.0</v>
-      </c>
-      <c r="J13" s="30">
-        <v>145873.0</v>
-      </c>
-      <c r="K13" s="30">
-        <v>17509.0</v>
-      </c>
-      <c r="L13" s="31">
-        <f t="shared" ref="L13:L14" si="1">SUM(C13:K13)</f>
+      <c r="C13" s="22">
+        <v>1750905</v>
+      </c>
+      <c r="D13" s="22">
+        <v>249095</v>
+      </c>
+      <c r="E13" s="23">
+        <v>148827</v>
+      </c>
+      <c r="F13" s="24">
+        <v>210108</v>
+      </c>
+      <c r="G13" s="25">
+        <v>9014</v>
+      </c>
+      <c r="H13" s="25">
+        <v>70036</v>
+      </c>
+      <c r="I13" s="25">
+        <v>145873</v>
+      </c>
+      <c r="J13" s="25">
+        <v>145873</v>
+      </c>
+      <c r="K13" s="25">
+        <v>17509</v>
+      </c>
+      <c r="L13" s="25">
+        <f t="shared" ref="L13:L14" si="0">SUM(C13:K13)</f>
         <v>2747240</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="s">
+    <row r="14" spans="1:12">
+      <c r="A14" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="32">
-        <v>2200000.0</v>
-      </c>
-      <c r="D14" s="28">
-        <v>249095.0</v>
-      </c>
-      <c r="E14" s="28">
-        <v>187000.0</v>
-      </c>
-      <c r="F14" s="33">
-        <v>264000.0</v>
-      </c>
-      <c r="G14" s="30">
-        <v>11484.0</v>
-      </c>
-      <c r="H14" s="30">
-        <v>88000.0</v>
-      </c>
-      <c r="I14" s="30">
-        <v>204000.0</v>
-      </c>
-      <c r="J14" s="30">
-        <v>204000.0</v>
-      </c>
-      <c r="K14" s="30">
-        <v>24049.0</v>
-      </c>
-      <c r="L14" s="31">
-        <f t="shared" si="1"/>
+      <c r="C14" s="26">
+        <v>2200000</v>
+      </c>
+      <c r="D14" s="23">
+        <v>249095</v>
+      </c>
+      <c r="E14" s="23">
+        <v>187000</v>
+      </c>
+      <c r="F14" s="27">
+        <v>264000</v>
+      </c>
+      <c r="G14" s="25">
+        <v>11484</v>
+      </c>
+      <c r="H14" s="25">
+        <v>88000</v>
+      </c>
+      <c r="I14" s="25">
+        <v>204000</v>
+      </c>
+      <c r="J14" s="25">
+        <v>204000</v>
+      </c>
+      <c r="K14" s="25">
+        <v>24049</v>
+      </c>
+      <c r="L14" s="25">
+        <f t="shared" si="0"/>
         <v>3431628</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="s">
+    <row r="15" spans="1:12">
+      <c r="A15" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="34">
-        <v>4000000.0</v>
-      </c>
-      <c r="D15" s="12" t="s">
+      <c r="C15" s="26">
+        <v>4000000</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="35">
-        <v>340000.0</v>
-      </c>
-      <c r="F15" s="36">
-        <v>480000.0</v>
-      </c>
-      <c r="G15" s="37">
-        <v>20000.0</v>
-      </c>
-      <c r="H15" s="37">
-        <v>160000.0</v>
-      </c>
-      <c r="I15" s="37">
-        <v>333200.0</v>
-      </c>
-      <c r="J15" s="38" t="s">
+      <c r="E15" s="28">
+        <v>340000</v>
+      </c>
+      <c r="F15" s="27">
+        <v>480000</v>
+      </c>
+      <c r="G15" s="25">
+        <v>20000</v>
+      </c>
+      <c r="H15" s="25">
+        <v>160000</v>
+      </c>
+      <c r="I15" s="25">
+        <v>333200</v>
+      </c>
+      <c r="J15" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="K15" s="39">
-        <v>40000.0</v>
-      </c>
-      <c r="L15" s="37">
-        <v>4886400.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="s">
+      <c r="K15" s="30">
+        <v>40000</v>
+      </c>
+      <c r="L15" s="25">
+        <v>4886400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="34">
-        <v>2500000.0</v>
-      </c>
-      <c r="D16" s="40" t="s">
+      <c r="C16" s="26">
+        <v>2500000</v>
+      </c>
+      <c r="D16" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="36">
-        <v>300000.0</v>
-      </c>
-      <c r="G16" s="37">
-        <v>12500.0</v>
-      </c>
-      <c r="H16" s="37">
-        <v>100000.0</v>
-      </c>
-      <c r="I16" s="37">
-        <v>208250.0</v>
-      </c>
-      <c r="J16" s="37">
-        <v>208250.0</v>
-      </c>
-      <c r="K16" s="37">
-        <v>25000.0</v>
-      </c>
-      <c r="L16" s="37">
-        <v>3216000.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="24"/>
+      <c r="F16" s="27">
+        <v>300000</v>
+      </c>
+      <c r="G16" s="25">
+        <v>12500</v>
+      </c>
+      <c r="H16" s="25">
+        <v>100000</v>
+      </c>
+      <c r="I16" s="25">
+        <v>208250</v>
+      </c>
+      <c r="J16" s="25">
+        <v>208250</v>
+      </c>
+      <c r="K16" s="25">
+        <v>25000</v>
+      </c>
+      <c r="L16" s="25">
+        <v>3216000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="18"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A4:F4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="C7"/>
-    <hyperlink r:id="rId2" ref="C8"/>
-    <hyperlink r:id="rId3" ref="C9"/>
-    <hyperlink r:id="rId4" ref="C10"/>
+    <hyperlink ref="C7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C8" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C10" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
-  <drawing r:id="rId5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:N38"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="21.5"/>
-    <col customWidth="1" min="2" max="2" width="20.63"/>
-    <col customWidth="1" min="3" max="3" width="21.5"/>
-    <col customWidth="1" min="4" max="4" width="18.5"/>
-    <col customWidth="1" min="9" max="9" width="18.88"/>
-    <col customWidth="1" min="10" max="10" width="20.25"/>
-    <col customWidth="1" min="11" max="11" width="24.13"/>
-    <col customWidth="1" min="12" max="12" width="24.5"/>
-    <col customWidth="1" min="14" max="14" width="18.63"/>
+    <col min="1" max="1" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" customWidth="1"/>
+    <col min="11" max="11" width="24.109375" customWidth="1"/>
+    <col min="12" max="12" width="24.44140625" customWidth="1"/>
+    <col min="14" max="14" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A1" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="42" t="s">
+      <c r="F1" s="54"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="41" t="s">
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="41" t="s">
+      <c r="N1" s="56" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="25" t="s">
+    <row r="2" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="45" t="s">
+      <c r="G2" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="I2" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="J2" s="45" t="s">
+      <c r="J2" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="K2" s="45" t="s">
+      <c r="K2" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="45" t="s">
+      <c r="L2" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="46" t="s">
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+    </row>
+    <row r="3" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A3" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="26">
-        <v>1750905.0</v>
-      </c>
-      <c r="D3" s="48">
-        <v>249095.0</v>
-      </c>
-      <c r="E3" s="29">
-        <v>210108.0</v>
-      </c>
-      <c r="F3" s="28">
-        <v>148827.0</v>
-      </c>
-      <c r="G3" s="30">
-        <v>9014.0</v>
-      </c>
-      <c r="H3" s="30">
-        <v>145873.0</v>
-      </c>
-      <c r="I3" s="30">
-        <v>145873.0</v>
-      </c>
-      <c r="J3" s="49">
-        <v>145873.0</v>
-      </c>
-      <c r="K3" s="49">
-        <v>17509.0</v>
-      </c>
-      <c r="L3" s="30">
-        <v>70036.0</v>
-      </c>
-      <c r="M3" s="47"/>
-      <c r="N3" s="50"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="46" t="s">
+      <c r="B3" s="34"/>
+      <c r="C3" s="22">
+        <v>1750905</v>
+      </c>
+      <c r="D3" s="35">
+        <v>249095</v>
+      </c>
+      <c r="E3" s="24">
+        <v>210108</v>
+      </c>
+      <c r="F3" s="23">
+        <v>148827</v>
+      </c>
+      <c r="G3" s="25">
+        <v>9014</v>
+      </c>
+      <c r="H3" s="25">
+        <v>145873</v>
+      </c>
+      <c r="I3" s="25">
+        <v>145873</v>
+      </c>
+      <c r="J3" s="36">
+        <v>145873</v>
+      </c>
+      <c r="K3" s="36">
+        <v>17509</v>
+      </c>
+      <c r="L3" s="25">
+        <v>70036</v>
+      </c>
+      <c r="M3" s="34"/>
+      <c r="N3" s="37"/>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A4" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="50"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="46" t="s">
+      <c r="B4" s="34"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="37"/>
+    </row>
+    <row r="5" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A5" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="50"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="46" t="s">
+      <c r="B5" s="34"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="37"/>
+    </row>
+    <row r="6" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A6" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="50"/>
-    </row>
-    <row r="8">
-      <c r="E8" s="59" t="s">
+      <c r="B6" s="40"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="37"/>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" customHeight="1">
+      <c r="E8" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="59" t="s">
+      <c r="F8" s="42" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="9">
-      <c r="E9" s="60" t="s">
+    <row r="9" spans="1:14" ht="15.75" customHeight="1">
+      <c r="E9" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="61" t="s">
+      <c r="F9" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="L9" s="62" t="s">
+      <c r="L9" s="59" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10">
-      <c r="E10" s="63" t="s">
+    <row r="10" spans="1:14" ht="15.75" customHeight="1">
+      <c r="E10" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="64">
-        <v>160.0</v>
-      </c>
-      <c r="L10" s="44"/>
-    </row>
-    <row r="11">
-      <c r="E11" s="65" t="s">
+      <c r="F10" s="46">
+        <v>160</v>
+      </c>
+      <c r="L10" s="57"/>
+    </row>
+    <row r="11" spans="1:14" ht="15.75" customHeight="1">
+      <c r="E11" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="66">
-        <v>20.0</v>
-      </c>
-      <c r="L11" s="67" t="s">
+      <c r="F11" s="48">
+        <v>20</v>
+      </c>
+      <c r="L11" s="49" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="12">
-      <c r="E12" s="63" t="s">
+    <row r="12" spans="1:14" ht="15.75" customHeight="1">
+      <c r="E12" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="68"/>
-      <c r="L12" s="67" t="s">
+      <c r="F12" s="46"/>
+      <c r="L12" s="49" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13">
-      <c r="E13" s="65" t="s">
+    <row r="13" spans="1:14" ht="15.75" customHeight="1">
+      <c r="E13" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="69"/>
-      <c r="L13" s="67" t="s">
+      <c r="F13" s="50"/>
+      <c r="L13" s="49" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14">
-      <c r="E14" s="63" t="s">
+    <row r="14" spans="1:14" ht="15.75" customHeight="1">
+      <c r="E14" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="68"/>
-      <c r="L14" s="67" t="s">
+      <c r="F14" s="46"/>
+      <c r="L14" s="49" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15">
-      <c r="E15" s="70"/>
-      <c r="F15" s="71"/>
-      <c r="L15" s="67" t="s">
+    <row r="15" spans="1:14" ht="15.75" customHeight="1">
+      <c r="E15" s="51"/>
+      <c r="F15" s="52"/>
+      <c r="L15" s="49" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="16">
-      <c r="E16" s="59" t="s">
+    <row r="16" spans="1:14" ht="15.75" customHeight="1">
+      <c r="E16" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="42" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="17">
-      <c r="E17" s="65" t="s">
+    <row r="17" spans="5:6" ht="15.75" customHeight="1">
+      <c r="E17" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="72" t="s">
+      <c r="F17" s="50" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="18">
-      <c r="E18" s="63" t="s">
+    <row r="18" spans="5:6" ht="15.75" customHeight="1">
+      <c r="E18" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="64">
-        <v>160.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="E19" s="65" t="s">
+      <c r="F18" s="46">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" spans="5:6" ht="15.75" customHeight="1">
+      <c r="E19" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="72" t="s">
+      <c r="F19" s="50" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20">
-      <c r="E20" s="63" t="s">
+    <row r="20" spans="5:6" ht="15.75" customHeight="1">
+      <c r="E20" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="F20" s="68"/>
-    </row>
-    <row r="21">
-      <c r="E21" s="65" t="s">
+      <c r="F20" s="46"/>
+    </row>
+    <row r="21" spans="5:6" ht="15.75" customHeight="1">
+      <c r="E21" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="F21" s="69"/>
-    </row>
-    <row r="22">
-      <c r="E22" s="63" t="s">
+      <c r="F21" s="50"/>
+    </row>
+    <row r="22" spans="5:6" ht="15.75" customHeight="1">
+      <c r="E22" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="68"/>
-    </row>
-    <row r="23">
-      <c r="E23" s="70"/>
-      <c r="F23" s="71"/>
-    </row>
-    <row r="24">
-      <c r="E24" s="59" t="s">
+      <c r="F22" s="46"/>
+    </row>
+    <row r="23" spans="5:6" ht="15.75" customHeight="1">
+      <c r="E23" s="51"/>
+      <c r="F23" s="52"/>
+    </row>
+    <row r="24" spans="5:6" ht="15.75" customHeight="1">
+      <c r="E24" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="59" t="s">
+      <c r="F24" s="42" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="25">
-      <c r="E25" s="60" t="s">
+    <row r="25" spans="5:6" ht="15.75" customHeight="1">
+      <c r="E25" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="F25" s="61" t="s">
+      <c r="F25" s="44" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="26">
-      <c r="E26" s="63" t="s">
+    <row r="26" spans="5:6" ht="15.75" customHeight="1">
+      <c r="E26" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="F26" s="64">
-        <v>160.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="E27" s="65" t="s">
+      <c r="F26" s="46">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="5:6" ht="15.75" customHeight="1">
+      <c r="E27" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F27" s="72" t="s">
+      <c r="F27" s="50" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="28">
-      <c r="E28" s="63" t="s">
+    <row r="28" spans="5:6" ht="14.4">
+      <c r="E28" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="F28" s="68"/>
-    </row>
-    <row r="29">
-      <c r="E29" s="65" t="s">
+      <c r="F28" s="46"/>
+    </row>
+    <row r="29" spans="5:6" ht="14.4">
+      <c r="E29" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="F29" s="69"/>
-    </row>
-    <row r="30">
-      <c r="E30" s="63" t="s">
+      <c r="F29" s="50"/>
+    </row>
+    <row r="30" spans="5:6" ht="14.4">
+      <c r="E30" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="F30" s="68"/>
-    </row>
-    <row r="31">
-      <c r="E31" s="70"/>
-      <c r="F31" s="71"/>
-    </row>
-    <row r="32">
-      <c r="E32" s="59" t="s">
+      <c r="F30" s="46"/>
+    </row>
+    <row r="31" spans="5:6" ht="14.4">
+      <c r="E31" s="51"/>
+      <c r="F31" s="52"/>
+    </row>
+    <row r="32" spans="5:6" ht="14.4">
+      <c r="E32" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="F32" s="59" t="s">
+      <c r="F32" s="42" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="33">
-      <c r="E33" s="60" t="s">
+    <row r="33" spans="5:6" ht="14.4">
+      <c r="E33" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="F33" s="73" t="s">
+      <c r="F33" s="44" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="34">
-      <c r="E34" s="63" t="s">
+    <row r="34" spans="5:6" ht="14.4">
+      <c r="E34" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="F34" s="64">
-        <v>160.0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="E35" s="65" t="s">
+      <c r="F34" s="46">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" spans="5:6" ht="14.4">
+      <c r="E35" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="72" t="s">
+      <c r="F35" s="50" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="36">
-      <c r="E36" s="63" t="s">
+    <row r="36" spans="5:6" ht="14.4">
+      <c r="E36" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="68"/>
-    </row>
-    <row r="37">
-      <c r="E37" s="65" t="s">
+      <c r="F36" s="46"/>
+    </row>
+    <row r="37" spans="5:6" ht="14.4">
+      <c r="E37" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="F37" s="69"/>
-    </row>
-    <row r="38">
-      <c r="E38" s="63" t="s">
+      <c r="F37" s="50"/>
+    </row>
+    <row r="38" spans="5:6" ht="14.4">
+      <c r="E38" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="F38" s="68"/>
+      <c r="F38" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="L9:L10"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:K1"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="L9:L10"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Planificacion/Costo_Estimado.xlsx
+++ b/Planificacion/Costo_Estimado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/93290c276c767585/Desktop/motogo/Planificacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_C4A46FE1E199D6D94E9442D8819BC8AF07816425" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C75073E5-D5D3-4D08-B522-2B8C2C69A123}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_C4A46FE1E199D6D94E9442D8819BC8AF07816425" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD2EF8EB-311C-4E7D-868B-38E009D5DCFF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
   <si>
     <t>Cuadro Comparativo de Cotizaciones para MOTOGO</t>
   </si>
@@ -264,9 +264,6 @@
   </si>
   <si>
     <t>$ 17.500,00</t>
-  </si>
-  <si>
-    <t>la mas perra</t>
   </si>
 </sst>
 </file>
@@ -711,10 +708,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -962,7 +959,7 @@
       <c r="F4" s="55"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" ht="13.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -971,7 +968,7 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" ht="13.2">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -992,7 +989,7 @@
       </c>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" ht="13.2">
       <c r="A7" s="8" t="s">
         <v>7</v>
       </c>
@@ -1013,7 +1010,7 @@
       </c>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" ht="13.2">
       <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
@@ -1034,7 +1031,7 @@
       </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" ht="13.2">
       <c r="A9" s="8" t="s">
         <v>18</v>
       </c>
@@ -1055,7 +1052,7 @@
       </c>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" ht="13.2">
       <c r="A10" s="8" t="s">
         <v>23</v>
       </c>
@@ -1076,7 +1073,7 @@
       </c>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" ht="13.2">
       <c r="A11" s="18"/>
       <c r="B11" s="17"/>
       <c r="C11" s="19"/>
@@ -1085,7 +1082,7 @@
       <c r="F11" s="20"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" ht="13.2">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -1123,7 +1120,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" ht="13.2">
       <c r="A13" s="8" t="s">
         <v>7</v>
       </c>
@@ -1162,7 +1159,7 @@
         <v>2747240</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" ht="13.2">
       <c r="A14" s="8" t="s">
         <v>13</v>
       </c>
@@ -1201,7 +1198,7 @@
         <v>3431628</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" ht="13.2">
       <c r="A15" s="8" t="s">
         <v>18</v>
       </c>
@@ -1239,7 +1236,7 @@
         <v>4886400</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" ht="13.2">
       <c r="A16" s="8" t="s">
         <v>23</v>
       </c>
@@ -1277,12 +1274,10 @@
         <v>3216000</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" ht="13.2">
       <c r="A17" s="18"/>
       <c r="B17" s="17"/>
-      <c r="C17" s="19" t="s">
-        <v>75</v>
-      </c>
+      <c r="C17" s="19"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
       <c r="F17" s="20"/>
@@ -1330,12 +1325,12 @@
       <c r="C1" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="58" t="s">
+      <c r="E1" s="59" t="s">
         <v>42</v>
       </c>
       <c r="F1" s="54"/>
       <c r="G1" s="55"/>
-      <c r="H1" s="58" t="s">
+      <c r="H1" s="59" t="s">
         <v>43</v>
       </c>
       <c r="I1" s="54"/>
@@ -1490,7 +1485,7 @@
       <c r="F9" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="L9" s="59" t="s">
+      <c r="L9" s="58" t="s">
         <v>61</v>
       </c>
     </row>
